--- a/data/availability/projects/the-waterway-developments/w55.xlsx
+++ b/data/availability/projects/the-waterway-developments/w55.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1709,7 +1709,6 @@
       <c r="G2" t="n">
         <v>185</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1720,7 +1719,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1766,7 +1765,6 @@
       <c r="G3" t="n">
         <v>185</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1777,7 +1775,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1823,7 +1821,6 @@
       <c r="G4" t="n">
         <v>185</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1834,7 +1831,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1880,7 +1877,6 @@
       <c r="G5" t="n">
         <v>185</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1891,7 +1887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1937,7 +1933,6 @@
       <c r="G6" t="n">
         <v>184</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -1948,7 +1943,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1994,7 +1989,6 @@
       <c r="G7" t="n">
         <v>184</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2005,7 +1999,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2051,7 +2045,6 @@
       <c r="G8" t="n">
         <v>184</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2062,7 +2055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2108,7 +2101,6 @@
       <c r="G9" t="n">
         <v>184</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2119,7 +2111,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2165,7 +2157,6 @@
       <c r="G10" t="n">
         <v>184</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2176,7 +2167,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2222,7 +2213,6 @@
       <c r="G11" t="n">
         <v>182</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2233,7 +2223,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2279,7 +2269,6 @@
       <c r="G12" t="n">
         <v>182</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2290,7 +2279,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2336,7 +2325,6 @@
       <c r="G13" t="n">
         <v>183</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2347,7 +2335,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2393,7 +2381,6 @@
       <c r="G14" t="n">
         <v>192</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2404,7 +2391,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2450,7 +2437,6 @@
       <c r="G15" t="n">
         <v>196</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2461,7 +2447,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2507,7 +2493,6 @@
       <c r="G16" t="n">
         <v>196</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2518,7 +2503,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2564,7 +2549,6 @@
       <c r="G17" t="n">
         <v>196</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2575,7 +2559,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2621,7 +2605,6 @@
       <c r="G18" t="n">
         <v>208</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2632,7 +2615,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2678,7 +2661,6 @@
       <c r="G19" t="n">
         <v>204</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2689,7 +2671,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2735,7 +2717,6 @@
       <c r="G20" t="n">
         <v>204</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2746,7 +2727,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2792,7 +2773,6 @@
       <c r="G21" t="n">
         <v>217</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2803,7 +2783,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2849,7 +2829,6 @@
       <c r="G22" t="n">
         <v>216</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2860,7 +2839,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2906,7 +2885,6 @@
       <c r="G23" t="n">
         <v>219</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2917,7 +2895,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2963,7 +2941,6 @@
       <c r="G24" t="n">
         <v>219</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -2974,7 +2951,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3020,7 +2997,6 @@
       <c r="G25" t="n">
         <v>219</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3031,7 +3007,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3077,7 +3053,6 @@
       <c r="G26" t="n">
         <v>223</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3088,7 +3063,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3134,7 +3109,6 @@
       <c r="G27" t="n">
         <v>219</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3145,7 +3119,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3191,7 +3165,6 @@
       <c r="G28" t="n">
         <v>223</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3202,7 +3175,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3248,7 +3221,6 @@
       <c r="G29" t="n">
         <v>227</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3259,7 +3231,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3305,7 +3277,6 @@
       <c r="G30" t="n">
         <v>227</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3316,7 +3287,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3362,7 +3333,6 @@
       <c r="G31" t="n">
         <v>231</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3373,7 +3343,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3419,7 +3389,6 @@
       <c r="G32" t="n">
         <v>231</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3430,7 +3399,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3476,7 +3445,6 @@
       <c r="G33" t="n">
         <v>231</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3487,7 +3455,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3533,7 +3501,6 @@
       <c r="G34" t="n">
         <v>231</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3544,7 +3511,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3590,7 +3557,6 @@
       <c r="G35" t="n">
         <v>242</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3601,7 +3567,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3647,7 +3613,6 @@
       <c r="G36" t="n">
         <v>240</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3658,7 +3623,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3704,7 +3669,6 @@
       <c r="G37" t="n">
         <v>240</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3715,7 +3679,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3761,7 +3725,6 @@
       <c r="G38" t="n">
         <v>235</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3772,7 +3735,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3818,7 +3781,6 @@
       <c r="G39" t="n">
         <v>255</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3829,7 +3791,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3875,7 +3837,6 @@
       <c r="G40" t="n">
         <v>255</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3886,7 +3847,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3932,7 +3893,6 @@
       <c r="G41" t="n">
         <v>255</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -3943,7 +3903,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3989,7 +3949,6 @@
       <c r="G42" t="n">
         <v>255</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4000,7 +3959,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4046,7 +4005,6 @@
       <c r="G43" t="n">
         <v>250</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4057,7 +4015,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4103,7 +4061,6 @@
       <c r="G44" t="n">
         <v>250</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4114,7 +4071,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4160,7 +4117,6 @@
       <c r="G45" t="n">
         <v>250</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4171,7 +4127,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4217,7 +4173,6 @@
       <c r="G46" t="n">
         <v>250</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4228,7 +4183,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4274,7 +4229,6 @@
       <c r="G47" t="n">
         <v>257</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4285,7 +4239,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4331,7 +4285,6 @@
       <c r="G48" t="n">
         <v>252</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4342,7 +4295,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4388,7 +4341,6 @@
       <c r="G49" t="n">
         <v>262</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4399,7 +4351,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4445,7 +4397,6 @@
       <c r="G50" t="n">
         <v>262</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4456,7 +4407,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4502,7 +4453,6 @@
       <c r="G51" t="n">
         <v>262</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4513,7 +4463,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4559,7 +4509,6 @@
       <c r="G52" t="n">
         <v>264</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4570,7 +4519,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4616,7 +4565,6 @@
       <c r="G53" t="n">
         <v>291</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4627,7 +4575,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4673,7 +4621,6 @@
       <c r="G54" t="n">
         <v>305</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4684,7 +4631,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4730,7 +4677,6 @@
       <c r="G55" t="n">
         <v>305</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4741,7 +4687,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4787,7 +4733,6 @@
       <c r="G56" t="n">
         <v>305</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Panoramic Views</t>
@@ -4798,7 +4743,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
